--- a/data/trans_dic/P55$familiar-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiar-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 33,5</t>
+          <t>7,24; 32,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 25,84</t>
+          <t>6,18; 26,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 36,19</t>
+          <t>8,82; 36,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,12; 50,06</t>
+          <t>27,64; 48,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,88; 30,45</t>
+          <t>12,26; 30,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,84; 39,7</t>
+          <t>19,44; 40,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 28,6</t>
+          <t>11,1; 28,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,83; 63,39</t>
+          <t>45,82; 62,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,02; 27,09</t>
+          <t>12,39; 27,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 31,93</t>
+          <t>15,57; 32,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,74; 26,44</t>
+          <t>11,84; 25,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,75; 55,28</t>
+          <t>40,43; 53,67</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 29,29</t>
+          <t>12,76; 29,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,77; 39,16</t>
+          <t>18,26; 36,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,92; 43,12</t>
+          <t>24,42; 42,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,27; 64,12</t>
+          <t>48,34; 63,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,84; 35,46</t>
+          <t>20,96; 35,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,64; 40,14</t>
+          <t>26,14; 39,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,11; 40,42</t>
+          <t>24,99; 39,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,1; 64,1</t>
+          <t>54,34; 62,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,18; 31,55</t>
+          <t>20,09; 31,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,92; 37,15</t>
+          <t>25,57; 36,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,93; 39,13</t>
+          <t>26,59; 38,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,97; 62,51</t>
+          <t>53,77; 61,56</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,87; 28,08</t>
+          <t>13,68; 27,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,53; 31,52</t>
+          <t>16,22; 31,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,89; 36,93</t>
+          <t>21,9; 36,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44,77; 57,02</t>
+          <t>43,59; 55,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,92; 31,99</t>
+          <t>19,9; 31,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,5; 37,72</t>
+          <t>26,4; 37,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,36; 34,74</t>
+          <t>22,32; 34,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,41; 62,18</t>
+          <t>53,59; 61,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,05; 28,18</t>
+          <t>19,27; 28,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,47; 33,37</t>
+          <t>24,25; 33,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,37; 33,24</t>
+          <t>23,35; 33,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52,79; 59,39</t>
+          <t>51,54; 58,16</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40036</t>
+          <t>43430</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59402</t>
+          <t>63980</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2999; 13998</t>
+          <t>3026; 13464</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2317; 11744</t>
+          <t>2809; 12136</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2745; 11342</t>
+          <t>2763; 11375</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14175; 25237</t>
+          <t>15220; 26802</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8036; 20604</t>
+          <t>8294; 20468</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13134; 27680</t>
+          <t>13556; 27933</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8510; 23491</t>
+          <t>9119; 23131</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34202; 46297</t>
+          <t>36890; 50169</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13156; 29645</t>
+          <t>13566; 30409</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18414; 36776</t>
+          <t>17934; 36986</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13327; 30005</t>
+          <t>13435; 29246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51534; 68248</t>
+          <t>54810; 72767</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60727</t>
+          <t>63897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>152172</t>
+          <t>162116</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>212899</t>
+          <t>226013</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10851; 24840</t>
+          <t>10821; 25232</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19910; 39442</t>
+          <t>18386; 36280</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21561; 38862</t>
+          <t>22006; 38376</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52552; 68391</t>
+          <t>55137; 72518</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34016; 57900</t>
+          <t>34216; 57564</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55900; 84228</t>
+          <t>54835; 82591</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46513; 74859</t>
+          <t>46285; 73266</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>140625; 163590</t>
+          <t>150380; 173798</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50064; 78270</t>
+          <t>49847; 77862</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80500; 115362</t>
+          <t>79415; 112823</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74149; 107754</t>
+          <t>73217; 107192</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>198919; 226215</t>
+          <t>210116; 240576</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80093</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>192209</t>
+          <t>205546</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>272302</t>
+          <t>289993</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17560; 35546</t>
+          <t>17321; 35325</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24159; 46071</t>
+          <t>23707; 45501</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26582; 44854</t>
+          <t>26604; 44783</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70318; 89567</t>
+          <t>73721; 94448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45999; 73873</t>
+          <t>45953; 73648</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74063; 105453</t>
+          <t>73799; 105405</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59795; 92871</t>
+          <t>59683; 92419</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>178607; 204104</t>
+          <t>191431; 218341</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>68120; 100743</t>
+          <t>68901; 101870</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104150; 142057</t>
+          <t>103211; 142669</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90859; 129260</t>
+          <t>90803; 128435</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>256200; 288244</t>
+          <t>271305; 306124</t>
         </is>
       </c>
     </row>
